--- a/Grout Stats/CI-PRO-001_REG-001 ROTURA DE GROUT 007.xlsx
+++ b/Grout Stats/CI-PRO-001_REG-001 ROTURA DE GROUT 007.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Powerchina\Tecnopilotes\Registros de Calidad\07 AG-10 (01-02-26)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C6D947-7885-433F-99F4-E14E0767261A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53EDA5EC-AFAD-4D01-A9DB-E9C2839660C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -199,21 +199,6 @@
     <t>Aerogenerador #10</t>
   </si>
   <si>
-    <t>TE-0142</t>
-  </si>
-  <si>
-    <t>TE-0143</t>
-  </si>
-  <si>
-    <t>TE-0144</t>
-  </si>
-  <si>
-    <t>TE-0145</t>
-  </si>
-  <si>
-    <t>TE-0146</t>
-  </si>
-  <si>
     <t>TE-153</t>
   </si>
   <si>
@@ -242,6 +227,21 @@
   </si>
   <si>
     <t>TE-156</t>
+  </si>
+  <si>
+    <t>TE-146</t>
+  </si>
+  <si>
+    <t>TE-145</t>
+  </si>
+  <si>
+    <t>TE-144</t>
+  </si>
+  <si>
+    <t>TE-143</t>
+  </si>
+  <si>
+    <t>TE-142</t>
   </si>
 </sst>
 </file>
@@ -1004,12 +1004,144 @@
     <xf numFmtId="4" fontId="7" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="distributed"/>
     </xf>
+    <xf numFmtId="4" fontId="7" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="distributed"/>
     </xf>
@@ -1042,138 +1174,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="distributed"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1788,162 +1788,162 @@
       </c>
       <c r="B1" s="65"/>
       <c r="C1" s="65"/>
-      <c r="D1" s="82" t="s">
+      <c r="D1" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="91" t="s">
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="86"/>
+      <c r="N1" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="92"/>
+      <c r="O1" s="94"/>
     </row>
     <row r="2" spans="1:20" ht="28.5" customHeight="1">
       <c r="A2" s="66"/>
       <c r="B2" s="67"/>
       <c r="C2" s="67"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="86"/>
-      <c r="L2" s="86"/>
-      <c r="M2" s="87"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="94"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="96"/>
     </row>
     <row r="3" spans="1:20" ht="43.5" customHeight="1">
       <c r="A3" s="66"/>
       <c r="B3" s="67"/>
       <c r="C3" s="67"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="93"/>
-      <c r="O3" s="94"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="91"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="95"/>
+      <c r="O3" s="96"/>
     </row>
     <row r="4" spans="1:20" ht="35.25" customHeight="1">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55" t="s">
+      <c r="B4" s="98"/>
+      <c r="C4" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="57"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="100"/>
+      <c r="H4" s="100"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="100"/>
+      <c r="K4" s="100"/>
+      <c r="L4" s="100"/>
+      <c r="M4" s="100"/>
+      <c r="N4" s="100"/>
+      <c r="O4" s="101"/>
     </row>
     <row r="5" spans="1:20" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A5" s="58" t="s">
+      <c r="A5" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="76" t="s">
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="78"/>
-      <c r="M5" s="79" t="s">
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
+      <c r="K5" s="79"/>
+      <c r="L5" s="80"/>
+      <c r="M5" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="80"/>
-      <c r="O5" s="81"/>
+      <c r="N5" s="82"/>
+      <c r="O5" s="83"/>
     </row>
     <row r="6" spans="1:20" ht="28.5" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="61"/>
-      <c r="E6" s="51" t="s">
+      <c r="D6" s="105"/>
+      <c r="E6" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="51" t="s">
+      <c r="F6" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="51" t="s">
+      <c r="G6" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="51" t="s">
+      <c r="H6" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="51" t="s">
+      <c r="I6" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="51" t="s">
+      <c r="J6" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="51" t="s">
+      <c r="K6" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="51" t="s">
+      <c r="L6" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="M6" s="51" t="s">
+      <c r="M6" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="N6" s="51" t="s">
+      <c r="N6" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="O6" s="51" t="s">
+      <c r="O6" s="76" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="36.75" customHeight="1" thickBot="1">
-      <c r="A7" s="52"/>
-      <c r="B7" s="52"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="52"/>
-      <c r="O7" s="52"/>
+      <c r="A7" s="77"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="106"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="77"/>
+      <c r="L7" s="77"/>
+      <c r="M7" s="77"/>
+      <c r="N7" s="77"/>
+      <c r="O7" s="77"/>
       <c r="Q7" s="5" t="s">
         <v>27</v>
       </c>
@@ -1962,12 +1962,12 @@
         <v>1</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="95" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="96"/>
+      <c r="D8" s="53"/>
       <c r="E8" s="24" t="s">
         <v>17</v>
       </c>
@@ -2026,12 +2026,12 @@
         <v>2</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="95" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="96"/>
+      <c r="D9" s="53"/>
       <c r="E9" s="24" t="s">
         <v>17</v>
       </c>
@@ -2074,12 +2074,12 @@
         <v>3</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="95" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="96"/>
+      <c r="D10" s="53"/>
       <c r="E10" s="24" t="s">
         <v>17</v>
       </c>
@@ -2122,12 +2122,12 @@
         <v>4</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="95" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="96"/>
+      <c r="D11" s="53"/>
       <c r="E11" s="24" t="s">
         <v>17</v>
       </c>
@@ -2170,12 +2170,12 @@
         <v>5</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="95" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="96"/>
+      <c r="D12" s="53"/>
       <c r="E12" s="24" t="s">
         <v>17</v>
       </c>
@@ -2230,12 +2230,12 @@
         <v>6</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="99" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="100"/>
+      <c r="D13" s="55"/>
       <c r="E13" s="30" t="s">
         <v>17</v>
       </c>
@@ -2294,12 +2294,12 @@
         <v>7</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="99" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="100"/>
+      <c r="D14" s="55"/>
       <c r="E14" s="30" t="s">
         <v>17</v>
       </c>
@@ -2342,12 +2342,12 @@
         <v>8</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="99" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="100"/>
+      <c r="D15" s="55"/>
       <c r="E15" s="30" t="s">
         <v>17</v>
       </c>
@@ -2390,12 +2390,12 @@
         <v>9</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="99" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="100"/>
+      <c r="D16" s="55"/>
       <c r="E16" s="30" t="s">
         <v>17</v>
       </c>
@@ -2438,12 +2438,12 @@
         <v>10</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="99" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="100"/>
+      <c r="D17" s="55"/>
       <c r="E17" s="30" t="s">
         <v>17</v>
       </c>
@@ -2498,12 +2498,12 @@
         <v>11</v>
       </c>
       <c r="B18" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="99" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="100"/>
+      <c r="D18" s="55"/>
       <c r="E18" s="30" t="s">
         <v>17</v>
       </c>
@@ -2562,12 +2562,12 @@
         <v>12</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="95" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="96"/>
+      <c r="D19" s="53"/>
       <c r="E19" s="24" t="s">
         <v>17</v>
       </c>
@@ -2596,7 +2596,7 @@
       <c r="M19" s="39">
         <v>246.5</v>
       </c>
-      <c r="N19" s="107">
+      <c r="N19" s="51">
         <f t="shared" si="3"/>
         <v>98.6</v>
       </c>
@@ -2610,12 +2610,12 @@
         <v>13</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="95" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="96"/>
+      <c r="D20" s="53"/>
       <c r="E20" s="24" t="s">
         <v>17</v>
       </c>
@@ -2658,12 +2658,12 @@
         <v>14</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="95" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="96"/>
+      <c r="D21" s="53"/>
       <c r="E21" s="24" t="s">
         <v>17</v>
       </c>
@@ -2706,12 +2706,12 @@
         <v>15</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="95" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="96"/>
+      <c r="D22" s="53"/>
       <c r="E22" s="24" t="s">
         <v>17</v>
       </c>
@@ -2752,8 +2752,8 @@
     <row r="23" spans="1:20" ht="39.75" customHeight="1" thickBot="1">
       <c r="A23" s="3"/>
       <c r="B23" s="4"/>
-      <c r="C23" s="97"/>
-      <c r="D23" s="98"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="60"/>
       <c r="E23" s="21"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
@@ -2803,25 +2803,25 @@
       <c r="O25" s="75"/>
     </row>
     <row r="26" spans="1:20" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A26" s="104" t="s">
+      <c r="A26" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="105"/>
-      <c r="C26" s="105"/>
-      <c r="D26" s="105"/>
-      <c r="E26" s="105"/>
-      <c r="F26" s="105"/>
-      <c r="G26" s="105"/>
-      <c r="H26" s="105"/>
-      <c r="I26" s="106"/>
-      <c r="J26" s="101" t="s">
+      <c r="B26" s="62"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="62"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="K26" s="102"/>
-      <c r="L26" s="102"/>
-      <c r="M26" s="102"/>
-      <c r="N26" s="102"/>
-      <c r="O26" s="103"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="58"/>
       <c r="P26" s="14"/>
       <c r="Q26" s="14"/>
     </row>
@@ -2923,21 +2923,16 @@
     <filterColumn colId="12" showButton="0"/>
   </autoFilter>
   <mergeCells count="41">
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="J26:O26"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:O4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="M6:M7"/>
     <mergeCell ref="A1:C3"/>
     <mergeCell ref="A24:O25"/>
     <mergeCell ref="A6:A7"/>
@@ -2954,16 +2949,21 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:O4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="J26:O26"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A26:I26"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
